--- a/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016</t>
+          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016 (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130397</t>
+          <t>130577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169950</t>
+          <t>168448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190370</t>
+          <t>190561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>237193</t>
+          <t>238815</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>333277</t>
+          <t>331940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393203</t>
+          <t>392482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97498</t>
+          <t>98115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133539</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127313</t>
+          <t>122538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168121</t>
+          <t>167476</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232546</t>
+          <t>233732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>290959</t>
+          <t>287518</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,08%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>272828</t>
+          <t>273101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>306271</t>
+          <t>308690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>422055</t>
+          <t>422824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>459424</t>
+          <t>459288</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>709003</t>
+          <t>707728</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>757939</t>
+          <t>756730</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>429815</t>
+          <t>430990</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>496552</t>
+          <t>496653</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434556</t>
+          <t>434363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>495091</t>
+          <t>497505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>882505</t>
+          <t>882063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>972945</t>
+          <t>975005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325897</t>
+          <t>325962</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>388644</t>
+          <t>386623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304762</t>
+          <t>300751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>364626</t>
+          <t>362070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>645586</t>
+          <t>647330</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>730986</t>
+          <t>733712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>856154</t>
+          <t>857304</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>916246</t>
+          <t>915999</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>778456</t>
+          <t>777680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>827534</t>
+          <t>828503</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1655919</t>
+          <t>1654862</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1731444</t>
+          <t>1730123</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,96%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96796</t>
+          <t>94831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127450</t>
+          <t>127588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87556</t>
+          <t>88864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118444</t>
+          <t>117038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192156</t>
+          <t>191483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>235816</t>
+          <t>236402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>60967</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88676</t>
+          <t>91819</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64273</t>
+          <t>64032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93132</t>
+          <t>92479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132583</t>
+          <t>131903</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176405</t>
+          <t>173522</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180780</t>
+          <t>180983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>207239</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145735</t>
+          <t>146087</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168670</t>
+          <t>170186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>333380</t>
+          <t>335402</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371390</t>
+          <t>370190</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,88%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>681204</t>
+          <t>685955</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>763323</t>
+          <t>768240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>742122</t>
+          <t>741283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>825762</t>
+          <t>826366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1443369</t>
+          <t>1449294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1564868</t>
+          <t>1570330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504862</t>
+          <t>505117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>581529</t>
+          <t>588413</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520103</t>
+          <t>513473</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>600080</t>
+          <t>598215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1047351</t>
+          <t>1048159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1155484</t>
+          <t>1159363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1337058</t>
+          <t>1336378</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1409155</t>
+          <t>1408075</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1374296</t>
+          <t>1367900</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1438983</t>
+          <t>1435044</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2733508</t>
+          <t>2727984</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2827503</t>
+          <t>2829733</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130577</t>
+          <t>131536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168448</t>
+          <t>169505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190561</t>
+          <t>191786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>238815</t>
+          <t>235952</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>331940</t>
+          <t>329940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>392482</t>
+          <t>394982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98115</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134131</t>
+          <t>133708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>122538</t>
+          <t>127923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167476</t>
+          <t>168243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>233732</t>
+          <t>232676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287518</t>
+          <t>288596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273101</t>
+          <t>270331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>308690</t>
+          <t>307210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>422824</t>
+          <t>421390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>459288</t>
+          <t>457437</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>707728</t>
+          <t>707424</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>756730</t>
+          <t>756973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>430990</t>
+          <t>433592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>496653</t>
+          <t>498579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434363</t>
+          <t>434248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>497505</t>
+          <t>496929</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>882063</t>
+          <t>885166</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>975005</t>
+          <t>977928</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,76%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386623</t>
+          <t>387819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300751</t>
+          <t>306138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362070</t>
+          <t>363925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>647330</t>
+          <t>648247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>733712</t>
+          <t>735331</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>857304</t>
+          <t>858778</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>915999</t>
+          <t>916939</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>777680</t>
+          <t>775086</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>828503</t>
+          <t>828489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1654862</t>
+          <t>1649579</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1730123</t>
+          <t>1729010</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94831</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127588</t>
+          <t>127475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88864</t>
+          <t>87355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117038</t>
+          <t>116764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191483</t>
+          <t>190332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>236402</t>
+          <t>233649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60967</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>91819</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64032</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92479</t>
+          <t>92462</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>131903</t>
+          <t>134313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173522</t>
+          <t>173661</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180983</t>
+          <t>181150</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206583</t>
+          <t>207608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>146087</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>170186</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>335402</t>
+          <t>334962</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370190</t>
+          <t>370730</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>685955</t>
+          <t>682509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>768240</t>
+          <t>770376</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>741283</t>
+          <t>737361</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>826366</t>
+          <t>823575</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1449294</t>
+          <t>1446894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1570330</t>
+          <t>1567298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>505117</t>
+          <t>504189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>588413</t>
+          <t>586174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513473</t>
+          <t>520207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598215</t>
+          <t>597990</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1048159</t>
+          <t>1048482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1159363</t>
+          <t>1157539</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1336378</t>
+          <t>1336757</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1408075</t>
+          <t>1410512</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1367900</t>
+          <t>1370593</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1435044</t>
+          <t>1436853</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2727984</t>
+          <t>2730687</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2829733</t>
+          <t>2825665</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Estudios-trans_orig.xlsx
@@ -828,112 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>293</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114959</t>
+          <t>290289</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95933</t>
+          <t>270331</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133708</t>
+          <t>307210</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>401</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>146243</t>
+          <t>442587</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127923</t>
+          <t>421390</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168243</t>
+          <t>457437</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>694</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>261202</t>
+          <t>732876</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>232676</t>
+          <t>707424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288596</t>
+          <t>756973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290289</t>
+          <t>114959</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>270331</t>
+          <t>95933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307210</t>
+          <t>133708</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>442587</t>
+          <t>146243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>421390</t>
+          <t>127923</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>457437</t>
+          <t>168243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>251</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>732876</t>
+          <t>261202</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>707424</t>
+          <t>232676</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>756973</t>
+          <t>288596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -1171,112 +1171,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>846</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>355897</t>
+          <t>888474</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325690</t>
+          <t>858778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>387819</t>
+          <t>916939</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>777</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>334025</t>
+          <t>802916</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>306138</t>
+          <t>775086</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363925</t>
+          <t>828489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1623</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>689922</t>
+          <t>1691389</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648247</t>
+          <t>1649579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>735331</t>
+          <t>1729010</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>80,91%</t>
         </is>
       </c>
     </row>
@@ -1284,112 +1284,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>335</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>888474</t>
+          <t>355897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>858778</t>
+          <t>325690</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>916939</t>
+          <t>387819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>325</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>802916</t>
+          <t>334025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>775086</t>
+          <t>306138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>828489</t>
+          <t>363925</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>660</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1691389</t>
+          <t>689922</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1649579</t>
+          <t>648247</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1729010</t>
+          <t>735331</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>34,41%</t>
         </is>
       </c>
     </row>
@@ -1514,112 +1514,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>178</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74261</t>
+          <t>195344</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60451</t>
+          <t>181150</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>207608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>152</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78293</t>
+          <t>158422</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>145508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>152554</t>
+          <t>353766</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>134313</t>
+          <t>334962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>173661</t>
+          <t>370730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
     </row>
@@ -1627,112 +1627,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>195344</t>
+          <t>74261</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>181150</t>
+          <t>60451</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>207608</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158422</t>
+          <t>78293</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>145508</t>
+          <t>64748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>168869</t>
+          <t>92462</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>353766</t>
+          <t>152554</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>334962</t>
+          <t>134313</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>370730</t>
+          <t>173661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -1857,112 +1857,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>545116</t>
+          <t>1374107</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>504189</t>
+          <t>1336757</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586174</t>
+          <t>1410512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>558561</t>
+          <t>1403925</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>520207</t>
+          <t>1370593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597990</t>
+          <t>1436853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1103678</t>
+          <t>2778032</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1048482</t>
+          <t>2730687</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1157539</t>
+          <t>2825665</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -1970,112 +1970,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>519</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1374107</t>
+          <t>545116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1336757</t>
+          <t>504189</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1410512</t>
+          <t>586174</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>536</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1403925</t>
+          <t>558561</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1370593</t>
+          <t>520207</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1436853</t>
+          <t>597990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2647</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2778032</t>
+          <t>1103678</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2730687</t>
+          <t>1048482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2825665</t>
+          <t>1157539</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
